--- a/assets/video/FORMULARIOS_APROY2026/FORM_POA_N°4_ACTIVIDADES_2026.xlsx
+++ b/assets/video/FORMULARIOS_APROY2026/FORM_POA_N°4_ACTIVIDADES_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilmer.mendoza\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp56\htdocs\siiplas_ci1.5\assets\video\FORMULARIOS_APROY2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -228,19 +228,13 @@
     <t>DEPARTAMENTO NACIONAL DE PLANIFICACION - CNS</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">UNIDAD RESPONSABLE: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Bookman Old Style"/>
-        <family val="1"/>
-      </rPr>
-      <t>DIRECCION CIMFA/CIS, UNIDAD RESPONSABLE (Ver Poa 2024 *)</t>
-    </r>
+    <t>META 2026</t>
+  </si>
+  <si>
+    <t>LINEA BASE 2025</t>
+  </si>
+  <si>
+    <t>PLAN OPERATIVO ANUAL 2027 - PROGRAMACIÓN FÍSICO FINANCIERO</t>
   </si>
   <si>
     <r>
@@ -254,7 +248,7 @@
         <rFont val="Bookman Old Style"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve"> REGIONAL (Ver Poa 2024 *)</t>
+      <t xml:space="preserve"> REGIONAL (Ver Poa 2026 *)</t>
     </r>
   </si>
   <si>
@@ -269,15 +263,12 @@
         <rFont val="Bookman Old Style"/>
         <family val="1"/>
       </rPr>
-      <t>DISTRITAL (Ver Poa 2024 *)</t>
+      <t>DISTRITAL (Ver Poa 2026 *)</t>
     </r>
   </si>
   <si>
-    <t>PLAN OPERATIVO ANUAL 2026 - PROGRAMACIÓN FÍSICO FINANCIERO</t>
-  </si>
-  <si>
     <r>
-      <t xml:space="preserve">CTA. PROGRAMATICA 2026 : </t>
+      <t xml:space="preserve">CTA. PROGRAMATICA 2027 : </t>
     </r>
     <r>
       <rPr>
@@ -287,14 +278,23 @@
         <rFont val="Bookman Old Style"/>
         <family val="1"/>
       </rPr>
-      <t>APERTURA - JEFATURA/ESTABLECIMIENTO  (Ver Poa 2024 *)</t>
+      <t>APERTURA - JEFATURA/ESTABLECIMIENTO  (Ver Poa 2026 *)</t>
     </r>
   </si>
   <si>
-    <t>META 2026</t>
-  </si>
-  <si>
-    <t>LINEA BASE 2025</t>
+    <r>
+      <t xml:space="preserve">UNIDAD RESPONSABLE: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Bookman Old Style"/>
+        <family val="1"/>
+      </rPr>
+      <t>DIRECCION CIMFA/CIS, UNIDAD RESPONSABLE (Ver Poa 2026 *)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -773,16 +773,6 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="5" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -812,6 +802,16 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="5" borderId="6" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="34">
@@ -883,7 +883,7 @@
         <xdr:cNvPr id="6" name="Imagen 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -933,7 +933,7 @@
         <xdr:cNvPr id="7" name="Conector recto 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -988,7 +988,7 @@
         <xdr:cNvPr id="8" name="Conector recto 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1043,7 +1043,7 @@
         <xdr:cNvPr id="9" name="CuadroTexto 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2851,104 +2851,104 @@
     </row>
     <row r="2" spans="1:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C2" s="3"/>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
+      <c r="T2" s="34"/>
+      <c r="U2" s="34"/>
+      <c r="V2" s="34"/>
+      <c r="W2" s="34"/>
     </row>
     <row r="3" spans="1:25" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="21"/>
       <c r="C3" s="22"/>
-      <c r="D3" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26"/>
-      <c r="V3" s="26"/>
-      <c r="W3" s="26"/>
+      <c r="D3" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="36"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="36"/>
+      <c r="T3" s="36"/>
+      <c r="U3" s="36"/>
+      <c r="V3" s="36"/>
+      <c r="W3" s="36"/>
       <c r="X3" s="23"/>
       <c r="Y3" s="23"/>
     </row>
     <row r="4" spans="1:25" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="3"/>
-      <c r="D4" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
+      <c r="D4" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
     </row>
     <row r="5" spans="1:25" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="3"/>
-      <c r="D5" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
+      <c r="D5" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
     </row>
     <row r="6" spans="1:25" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="3"/>
-      <c r="D6" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
+      <c r="D6" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
     </row>
     <row r="7" spans="1:25" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="3"/>
-      <c r="D7" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
+      <c r="D7" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
     </row>
     <row r="8" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="3"/>
@@ -2957,10 +2957,10 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:25" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="7" t="s">
@@ -2969,46 +2969,46 @@
       <c r="D9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="E9" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="32"/>
-      <c r="G9" s="33" t="s">
+      <c r="F9" s="29"/>
+      <c r="G9" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="33" t="s">
+      <c r="H9" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="33" t="s">
+      <c r="I9" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="J9" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="K9" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="L9" s="35" t="s">
+      <c r="J9" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
-      <c r="S9" s="36"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="36"/>
-      <c r="V9" s="36"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="27" t="s">
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33"/>
+      <c r="P9" s="33"/>
+      <c r="Q9" s="33"/>
+      <c r="R9" s="33"/>
+      <c r="S9" s="33"/>
+      <c r="T9" s="33"/>
+      <c r="U9" s="33"/>
+      <c r="V9" s="33"/>
+      <c r="W9" s="33"/>
+      <c r="X9" s="24" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="29"/>
-      <c r="B10" s="30"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="8" t="s">
         <v>23</v>
       </c>
@@ -3021,11 +3021,11 @@
       <c r="F10" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="34"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
       <c r="L10" s="10" t="s">
         <v>3</v>
       </c>
@@ -3062,7 +3062,7 @@
       <c r="W10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="X10" s="27"/>
+      <c r="X10" s="24"/>
     </row>
     <row r="11" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
@@ -3420,6 +3420,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="D2:W2"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D3:W3"/>
     <mergeCell ref="X9:X10"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
@@ -3430,12 +3436,6 @@
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="L9:W9"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="D2:W2"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D3:W3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H9"/>
